--- a/artfynd/A 37581-2026 artfynd.xlsx
+++ b/artfynd/A 37581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583112</v>
       </c>
       <c r="B2" t="n">
-        <v>79231</v>
+        <v>79233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37581-2026 artfynd.xlsx
+++ b/artfynd/A 37581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583112</v>
       </c>
       <c r="B2" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37581-2026 artfynd.xlsx
+++ b/artfynd/A 37581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583112</v>
       </c>
       <c r="B2" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37581-2026 artfynd.xlsx
+++ b/artfynd/A 37581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583112</v>
       </c>
       <c r="B2" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37581-2026 artfynd.xlsx
+++ b/artfynd/A 37581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583112</v>
       </c>
       <c r="B2" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 37581-2026 artfynd.xlsx
+++ b/artfynd/A 37581-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136583112</v>
       </c>
       <c r="B2" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
